--- a/data/trans_orig/IP1004-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP1004-Habitat-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3603</t>
+          <t>3677</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3849</t>
+          <t>2964</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>135123</t>
+          <t>135049</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>287954</t>
+          <t>288839</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>617</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>6096</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>619</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6236</t>
+          <t>5851</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>205632</t>
+          <t>206046</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>211441</t>
+          <t>211525</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>401069</t>
+          <t>401454</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>406684</t>
+          <t>406686</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3387</t>
+          <t>3842</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3929</t>
+          <t>3388</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>146270</t>
+          <t>145815</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>283545</t>
+          <t>284086</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3429</t>
+          <t>3099</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3722</t>
+          <t>2986</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,72%</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>205886</t>
+          <t>206216</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>413417</t>
+          <t>414153</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4343</t>
+          <t>4247</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6886</t>
+          <t>7731</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1918</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8974</t>
+          <t>8788</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>676678</t>
+          <t>676774</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>715814</t>
+          <t>714969</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>721513</t>
+          <t>721434</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1394747</t>
+          <t>1394933</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1401803</t>
+          <t>1401718</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5119</t>
+          <t>3712</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4298</t>
+          <t>4658</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>160866</t>
+          <t>162273</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>316526</t>
+          <t>316166</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4762</t>
+          <t>4696</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3728,7 +3728,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>5300</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6111</t>
+          <t>6205</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>205538</t>
+          <t>205604</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>201781</t>
+          <t>201782</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>411271</t>
+          <t>411177</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>416644</t>
+          <t>417382</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>100,0%</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3959</t>
+          <t>4960</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>745</t>
+          <t>749</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7074</t>
+          <t>6483</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>855</t>
+          <t>791</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7863</t>
+          <t>8042</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -4164,7 +4164,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>702969</t>
+          <t>701968</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>741068</t>
+          <t>741659</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>747397</t>
+          <t>747393</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1447207</t>
+          <t>1447028</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1454215</t>
+          <t>1454279</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,94%</t>
+          <t>99,95%</t>
         </is>
       </c>
     </row>
@@ -4631,7 +4631,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4146</t>
+          <t>4817</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4519</t>
+          <t>4714</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -4739,7 +4739,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>129561</t>
+          <t>128890</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4754,7 +4754,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>277264</t>
+          <t>277069</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5276</t>
+          <t>4776</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4354</t>
+          <t>4712</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,33%</t>
         </is>
       </c>
     </row>
@@ -6111,7 +6111,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>699095</t>
+          <t>699595</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -6181,7 +6181,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1444861</t>
+          <t>1444503</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">

--- a/data/trans_orig/IP1004-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP1004-Habitat-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,107 +722,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>732</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3677</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4903</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,53%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,65%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>3,53%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>732</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3680</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,25%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>732</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>2964</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -835,74 +835,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>202</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>137994</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>135049</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>133823</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>138726</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>99,47%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>97,35%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>96,47%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>428</t>
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>288839</t>
+          <t>288123</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>203</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,92 +1065,92 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2582</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>620</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>6269</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,22%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2,96%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>2582</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>617</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>6096</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,22%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>2,87%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>2582</t>
-        </is>
-      </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>701</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5851</t>
+          <t>6821</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -1178,72 +1178,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>318</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>209560</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>205873</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>211522</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,78%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>97,04%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,71%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>312</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>195163</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>318</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>209560</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>206046</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>211525</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,78%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>401454</t>
+          <t>400484</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>406686</t>
+          <t>406604</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,83%</t>
         </is>
       </c>
     </row>
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>312</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,107 +1408,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3486</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2,33%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>673</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3842</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>3372</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,23%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>2,57%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>673</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>3388</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -1521,72 +1521,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>148984</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>146171</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,55%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>97,67%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>137817</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>148984</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>145815</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,55%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>284086</t>
+          <t>284102</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,107 +1751,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>683</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3099</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4567</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,33%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1,48%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>2,18%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>683</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>3433</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>683</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>2986</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -1864,74 +1864,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>273</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>208632</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>206216</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>204748</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>209315</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,67%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>98,52%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>97,82%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>579</t>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>414153</t>
+          <t>413706</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>274</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,72 +2094,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3255</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1187</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>7372</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>1415</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4247</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>4515</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,21%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>3255</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>1266</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>7731</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2003</t>
+          <t>1729</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8788</t>
+          <t>9392</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -2207,74 +2207,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>719445</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>715328</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>721513</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,55%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>98,98%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,84%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1016</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>679606</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>676774</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>676506</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,79%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>99,38%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>99,34%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>719445</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>714969</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>721434</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,55%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>98,93%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,82%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>2097</t>
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1394933</t>
+          <t>1394329</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1401718</t>
+          <t>1401992</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,88%</t>
         </is>
       </c>
     </row>
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1086</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1086</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2501,7 +2501,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2782,47 +2782,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>153098</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>185</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>136391</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>153098</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>153098</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>153098</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>153098</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>185</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>136391</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>136391</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>136391</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>153098</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>153098</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>153098</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3125,47 +3125,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>221977</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>317</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>205398</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>321</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>221977</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>221977</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>221977</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>221977</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>317</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>205398</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>205398</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>205398</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>321</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>221977</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>221977</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>221977</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3355,107 +3355,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>857</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4554</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2,74%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>857</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3712</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>4341</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>2,24%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>857</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>4658</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,35%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>165128</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>161431</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>165985</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,48%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>97,26%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>154839</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>165128</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>162273</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>165985</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,48%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>316166</t>
+          <t>316483</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>165985</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>165985</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>165985</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>154839</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>154839</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>154839</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>165985</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>165985</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>165985</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3698,72 +3698,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1522</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4659</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,73%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,25%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>790</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4696</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3980</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,38%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,23%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1522</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5300</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>743</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6205</t>
+          <t>6202</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -3811,74 +3811,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>205560</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>202423</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>207082</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,27%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>97,75%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>274</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>209510</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>205604</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>206320</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>210300</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,62%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>97,77%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>98,11%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>279</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>205560</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>201782</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>207082</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,27%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>97,44%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>553</t>
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>411177</t>
+          <t>411180</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>417382</t>
+          <t>416639</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3911,7 +3911,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,82%</t>
         </is>
       </c>
     </row>
@@ -3924,57 +3924,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>207082</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>207082</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>207082</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>275</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>210300</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>210300</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>210300</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>207082</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>207082</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>207082</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4041,72 +4041,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2379</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>745</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>6347</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>790</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4960</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>4559</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,11%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>2379</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>749</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>6483</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>791</t>
+          <t>853</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8042</t>
+          <t>8280</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,57%</t>
         </is>
       </c>
     </row>
@@ -4154,74 +4154,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1063</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>745763</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>741795</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>747397</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,68%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>99,15%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,9%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1017</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>706138</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>701968</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>702369</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,89%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>99,3%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>99,36%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1063</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>745763</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>741659</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>747393</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,68%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>99,13%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,9%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>2080</t>
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1447028</t>
+          <t>1446790</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1454279</t>
+          <t>1454217</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,95%</t>
+          <t>99,94%</t>
         </is>
       </c>
     </row>
@@ -4267,57 +4267,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1066</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4448,7 +4448,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4616,107 +4616,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>1360</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4817</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5074</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>1,02%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,6%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>3,8%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1360</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>5110</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1360</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4714</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -4729,74 +4729,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>185</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>132347</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>128890</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>128633</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>133707</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>98,98%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>96,4%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>96,2%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>380</t>
@@ -4809,7 +4809,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>277069</t>
+          <t>276673</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4842,57 +4842,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5072,47 +5072,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>334</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>207247</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>332</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -5185,57 +5185,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>334</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>207247</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>207247</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>207247</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>332</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5415,47 +5415,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>259</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>155997</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -5528,57 +5528,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>259</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5758,47 +5758,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>281</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>207420</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>290</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -5871,57 +5871,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>281</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>207420</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>207420</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>207420</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>290</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5988,92 +5988,92 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>1360</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4776</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5576</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,19%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>1360</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1360</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4712</t>
+          <t>4825</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6101,74 +6101,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1059</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>703011</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>699595</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>698795</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,81%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>99,32%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>99,21%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>2124</t>
@@ -6181,7 +6181,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1444503</t>
+          <t>1444390</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -6214,57 +6214,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
